--- a/Data/EXCEL/Transfer/salemon/20240711/3673-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/3673-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51E47542-C95F-4170-8C76-033F463452F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F311F544-A5FB-4482-9D38-19DC79394A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1040" windowWidth="18240" windowHeight="13390" xr2:uid="{912F63D7-C938-4C0E-A6B3-0225243A39AB}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{BC889C75-069E-414E-BA56-650E18CED8F4}"/>
   </bookViews>
   <sheets>
     <sheet name="3673-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1267,24 +1267,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6C11C6-E112-4B18-BD44-86D536FB9F63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC53A021-22EC-42C1-AE63-CB0E5D30CA9D}">
   <dimension ref="A1:Q344"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="22"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="17" t="s">
         <v>4</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1393,7 +1393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>-5.46</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>-7.99</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>-9.1999999999999993</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>-4.42</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>-28.1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>-30.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>-31.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>-30.9</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>-30.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>-29.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>-28.2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>-28.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>-25.3</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>-28.9</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>-5.73</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>-3.15</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>-4.51</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>-6.01</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>-8.77</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>-15.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>-25.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>-29.3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>-11.7</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>44440</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>-9.7799999999999994</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>44378</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>-8.15</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>-4.38</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>44317</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>-2.15</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44256</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>44197</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>-16.100000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>44136</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>-16.600000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>44075</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>-7.47</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>44013</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>-5.07</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>-5.64</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>43952</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>-4.38</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>-3.35</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>43891</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>-9.51</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>43831</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>-32.200000000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>43770</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>43709</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>43647</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>43586</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>43525</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>43466</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>43405</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>43344</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>-6.49</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>43282</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>43221</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>-6.63</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>-1.47</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>43160</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>-2.62</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>43101</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>43040</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>42979</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>42917</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>42856</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>42795</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>-1.83</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>42736</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>-26.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>42675</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>-29.1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>-27.9</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>42614</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>42552</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>-26.5</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>-27.3</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>42491</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>-28.5</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>-26.8</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>42430</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>42370</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>-6.29</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>42309</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>-2.29</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>-1.82</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>42248</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>-3.34</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>-5.67</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>42186</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>-8.42</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>-8.08</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>42125</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>-1.78</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>42064</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>-1.51</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>42005</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>-4.76</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>-18.600000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>41944</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>-19.899999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>41883</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>-23.2</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>-26.3</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>41821</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>-34.6</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>41760</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>-41.2</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>41699</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>-46.2</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>-44.7</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>41640</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>-41.4</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>-9.93</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>41579</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>-7.18</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>-1.9</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>41518</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>41456</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>41395</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>41334</v>
       </c>
@@ -8640,7 +8640,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>41275</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>41214</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>41183</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>41153</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>41122</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>41091</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>41061</v>
       </c>
@@ -9117,7 +9117,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>41030</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>41000</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>40969</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>59.8</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>40940</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>40909</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>40878</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>140.6</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>40848</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>142.19999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>40817</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>165.6</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>40787</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>199.1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>40756</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>215.2</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>40725</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>246.2</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>40695</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>272.5</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>40664</v>
       </c>
@@ -9806,7 +9806,7 @@
         <v>304.7</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>40634</v>
       </c>
@@ -9859,7 +9859,7 @@
         <v>358.2</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>40603</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>398.6</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>40575</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>430.8</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>40544</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>325.7</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>40513</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>40483</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>200.4</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>40452</v>
       </c>
@@ -10177,877 +10177,877 @@
         <v>160.9</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>44075</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="9">
         <v>43344</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="9">
         <v>43282</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="9">
         <v>43221</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="9">
         <v>43160</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="9">
         <v>43101</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="9">
         <v>43040</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="9">
         <v>42979</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="9">
         <v>42917</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="9">
         <v>42856</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="9">
         <v>42795</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="9">
         <v>42736</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="9">
         <v>42675</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="9">
         <v>42614</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="9">
         <v>42552</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="9">
         <v>42491</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="9">
         <v>42430</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="9">
         <v>42370</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="9">
         <v>42309</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="9">
         <v>42248</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="9">
         <v>42186</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="9">
         <v>42125</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="9">
         <v>42064</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="9">
         <v>42005</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="9">
         <v>41944</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="9">
         <v>41883</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" s="9">
         <v>41821</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" s="9">
         <v>41760</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" s="9">
         <v>41699</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" s="9">
         <v>41640</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" s="9">
         <v>41579</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" s="9">
         <v>41518</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" s="9">
         <v>41456</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" s="9">
         <v>41395</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" s="9">
         <v>41334</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" s="9">
         <v>41275</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" s="5">
         <v>41244</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" s="9">
         <v>41214</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" s="5">
         <v>41183</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" s="9">
         <v>41153</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" s="5">
         <v>41122</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="9">
         <v>41091</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="5">
         <v>41061</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="9">
         <v>41030</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="5">
         <v>41000</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="9">
         <v>40969</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="5">
         <v>40940</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="9">
         <v>40909</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="5">
         <v>40878</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="9">
         <v>40848</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="5">
         <v>40817</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" s="9">
         <v>40787</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" s="5">
         <v>40756</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" s="9">
         <v>40725</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" s="5">
         <v>40695</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" s="9">
         <v>40664</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" s="5">
         <v>40634</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" s="9">
         <v>40603</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" s="5">
         <v>40575</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" s="9">
         <v>40544</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" s="5">
         <v>40513</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" s="9">
         <v>40483</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" s="5">
         <v>40452</v>
       </c>
